--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N110_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N110_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>81.26379342385006</v>
+        <v>13.20536643137564</v>
       </c>
       <c r="D2" t="n">
-        <v>80.90137926803604</v>
+        <v>13.14647413105586</v>
       </c>
       <c r="E2" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F2" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.93260495977988</v>
+        <v>4.214048305964231</v>
       </c>
       <c r="D3" t="n">
-        <v>26.15984792316814</v>
+        <v>4.250975287514822</v>
       </c>
       <c r="E3" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F3" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.145764971629156</v>
+        <v>1.323686807889738</v>
       </c>
       <c r="D4" t="n">
-        <v>8.154328083624296</v>
+        <v>1.325078313588948</v>
       </c>
       <c r="E4" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F4" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.42027258550798</v>
+        <v>3.480794295145047</v>
       </c>
       <c r="D5" t="n">
-        <v>21.63441153532403</v>
+        <v>3.515591874490155</v>
       </c>
       <c r="E5" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F5" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.22156680269352</v>
+        <v>5.723504605437697</v>
       </c>
       <c r="D6" t="n">
-        <v>35.32249776237118</v>
+        <v>5.739905886385317</v>
       </c>
       <c r="E6" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F6" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>4.512732552635709</v>
+        <v>0.7333190398033028</v>
       </c>
       <c r="D7" t="n">
-        <v>4.150489192702318</v>
+        <v>0.6744544938141266</v>
       </c>
       <c r="E7" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F7" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.18899255070613</v>
+        <v>2.793211289489746</v>
       </c>
       <c r="D8" t="n">
-        <v>16.9598691477632</v>
+        <v>2.75597873651152</v>
       </c>
       <c r="E8" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F8" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.87124745337126</v>
+        <v>5.17907771117283</v>
       </c>
       <c r="D9" t="n">
-        <v>31.99837179854172</v>
+        <v>5.19973541726303</v>
       </c>
       <c r="E9" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F9" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.47174197841945</v>
+        <v>3.164158071493161</v>
       </c>
       <c r="D10" t="n">
-        <v>19.08846294706821</v>
+        <v>3.101875228898583</v>
       </c>
       <c r="E10" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F10" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>35.56917359501639</v>
+        <v>5.779990709190163</v>
       </c>
       <c r="D11" t="n">
-        <v>35.94612229296328</v>
+        <v>5.841244872606533</v>
       </c>
       <c r="E11" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F11" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>57.18791299419897</v>
+        <v>9.293035861557332</v>
       </c>
       <c r="D12" t="n">
-        <v>56.78322624880617</v>
+        <v>9.227274265431003</v>
       </c>
       <c r="E12" t="n">
-        <v>21.13970908088718</v>
+        <v>3.435202725644166</v>
       </c>
       <c r="F12" t="n">
-        <v>21.08566100482244</v>
+        <v>3.426419913283647</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
